--- a/data/trans_dic/IP28_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 6,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,42</t>
+          <t>0,91; 7,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,13</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,79; 7,94</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,86</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 7,5</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0; 2,74</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,94; 8,23</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,63</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,81</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,18</t>
+          <t>1,11; 5,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,52</t>
+          <t>0,89; 5,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,05</t>
+          <t>0,57; 5,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,16</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,56</t>
+          <t>0,69; 2,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,55</t>
+          <t>1,16; 3,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,22</t>
+          <t>0,42; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,12</t>
+          <t>0,84; 3,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,28</t>
+          <t>0,56; 2,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,04</t>
+          <t>0,9; 3,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,02</t>
+          <t>0,46; 2,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,14</t>
+          <t>0,42; 2,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,02</t>
+          <t>0,81; 1,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,87</t>
+          <t>1,29; 2,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,78</t>
+          <t>0,6; 1,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,19</t>
+          <t>0,79; 2,09</t>
         </is>
       </c>
     </row>
@@ -996,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,04</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,4; 3,61</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,87</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 3,65</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,14</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,67</t>
+          <t>0,2; 1,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,88</t>
+          <t>0,45; 2,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,64</t>
+          <t>0,19; 1,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,17</t>
+          <t>0,23; 2,05</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,17</t>
+          <t>0,72; 2,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,03</t>
+          <t>1,16; 3,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,81</t>
+          <t>0,5; 1,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,7</t>
+          <t>0,77; 2,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,18</t>
+          <t>0,66; 2,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,62</t>
+          <t>0,98; 2,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,73</t>
+          <t>0,49; 1,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,78</t>
+          <t>0,49; 1,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,88</t>
+          <t>0,83; 1,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,5</t>
+          <t>1,29; 2,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,55</t>
+          <t>0,62; 1,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,85</t>
+          <t>0,76; 1,78</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1628</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2795</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2764</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4392</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4043</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2079</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5406</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>750; 6545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4099</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>685; 6846</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4429</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4559</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4887</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1948; 9326</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1407; 8874</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>630; 5716</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4704</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8742</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4276</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7830</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8063</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>11231</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16805</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8986</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>13077</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2832; 10352</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4740; 15598</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1800; 8348</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3849; 13883</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2657; 10709</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4046; 13758</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2001; 9468</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2184; 11016</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7175; 17487</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>11061; 23936</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5149; 15504</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7641; 20279</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5903</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5344</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4279</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5835</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3203</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>648; 5909</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3158</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4358</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>638; 5340</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1416; 8393</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>619; 5321</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>776; 6793</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13052</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6372</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7453</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24471</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>16995</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4849; 15464</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7527; 20054</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3196; 11478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5091; 16866</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4721; 14472</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>6770; 18142</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3251; 11437</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3703; 13771</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11460; 24919</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>17182; 33541</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8073; 19699</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>10841; 25321</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP28_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,04</t>
+          <t>0,0; 6,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,93</t>
+          <t>0,92; 8,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 7,94</t>
+          <t>0,78; 8,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,86</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,31</t>
+          <t>0,84; 5,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,61</t>
+          <t>0,87; 5,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,14</t>
+          <t>0,56; 5,04</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,52</t>
+          <t>0,68; 2,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,81</t>
+          <t>1,16; 3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,96</t>
+          <t>0,41; 1,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,04</t>
+          <t>0,78; 3,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,27</t>
+          <t>0,57; 2,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,06</t>
+          <t>0,92; 3,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,16</t>
+          <t>0,46; 2,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,14</t>
+          <t>0,39; 2,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,98</t>
+          <t>0,73; 1,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,79</t>
+          <t>1,28; 2,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,8</t>
+          <t>0,58; 1,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,09</t>
+          <t>0,83; 2,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,47</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,61</t>
+          <t>0,4; 3,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,64</t>
+          <t>0,2; 1,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,64</t>
+          <t>0,44; 2,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,63</t>
+          <t>0,19; 1,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,05</t>
+          <t>0,23; 2,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,31</t>
+          <t>0,73; 2,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,1</t>
+          <t>1,28; 3,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,81</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,55</t>
+          <t>0,74; 2,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,02</t>
+          <t>0,7; 2,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,63</t>
+          <t>1,04; 2,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,71</t>
+          <t>0,49; 1,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,82</t>
+          <t>0,49; 1,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,8</t>
+          <t>0,82; 1,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,51</t>
+          <t>1,3; 2,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,51</t>
+          <t>0,63; 1,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,78</t>
+          <t>0,74; 1,85</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5406</t>
+          <t>0; 5420</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>750; 6545</t>
+          <t>759; 6696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4099</t>
+          <t>0; 3664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1524,42 +1524,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>685; 6846</t>
+          <t>673; 7070</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4429</t>
+          <t>0; 3857</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4559</t>
+          <t>0; 4662</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4887</t>
+          <t>0; 5168</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1948; 9326</t>
+          <t>1478; 9250</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1407; 8874</t>
+          <t>1371; 8175</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>630; 5716</t>
+          <t>626; 5604</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4704</t>
+          <t>0; 4448</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2832; 10352</t>
+          <t>2801; 11140</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4740; 15598</t>
+          <t>4757; 14665</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1800; 8348</t>
+          <t>1759; 8492</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3849; 13883</t>
+          <t>3582; 14406</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2657; 10709</t>
+          <t>2681; 10458</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4046; 13758</t>
+          <t>4112; 13807</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2001; 9468</t>
+          <t>2012; 9595</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2184; 11016</t>
+          <t>1999; 10416</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7175; 17487</t>
+          <t>6423; 17354</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11061; 23936</t>
+          <t>11003; 24016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5149; 15504</t>
+          <t>4969; 14647</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7641; 20279</t>
+          <t>8022; 21161</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5903</t>
+          <t>0; 4705</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5344</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4279</t>
+          <t>0; 4099</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5835</t>
+          <t>0; 5668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3203</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>648; 5909</t>
+          <t>654; 5744</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3158</t>
+          <t>0; 3520</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4358</t>
+          <t>0; 4294</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>638; 5340</t>
+          <t>638; 5650</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1416; 8393</t>
+          <t>1406; 7908</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>619; 5321</t>
+          <t>624; 5279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>776; 6793</t>
+          <t>768; 7097</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4849; 15464</t>
+          <t>4925; 14519</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7527; 20054</t>
+          <t>8273; 19521</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3196; 11478</t>
+          <t>3221; 11189</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5091; 16866</t>
+          <t>4921; 17184</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4721; 14472</t>
+          <t>5016; 14699</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6770; 18142</t>
+          <t>7140; 18015</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3251; 11437</t>
+          <t>3262; 11672</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3703; 13771</t>
+          <t>3723; 13517</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11460; 24919</t>
+          <t>11313; 24959</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17182; 33541</t>
+          <t>17317; 34048</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8073; 19699</t>
+          <t>8150; 20111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10841; 25321</t>
+          <t>10516; 26295</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP28_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,82%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,06</t>
+          <t>0,94; 8,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,11</t>
+          <t>0,0; 6,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 6,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 10,33</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,21</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,92; 8,42</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,5</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,78; 8,2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,67</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,33</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,26</t>
+          <t>1,02; 5,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,17</t>
+          <t>0,89; 5,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,04</t>
+          <t>0,56; 5,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,13%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,71</t>
+          <t>0,55; 2,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,58</t>
+          <t>0,97; 3,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,99</t>
+          <t>0,46; 2,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,15</t>
+          <t>0,44; 2,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,22</t>
+          <t>0,68; 2,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,07</t>
+          <t>1,13; 3,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,19</t>
+          <t>0,42; 2,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,02</t>
+          <t>1,05; 3,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,96</t>
+          <t>0,77; 2,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,8</t>
+          <t>1,27; 2,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,7</t>
+          <t>0,6; 1,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,18</t>
+          <t>0,92; 2,36</t>
         </is>
       </c>
     </row>
@@ -929,54 +929,54 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,4; 3,65</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,14</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,87</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,89</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,47</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,99</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,61</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,79</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,45</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,4; 3,51</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,08</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,73</t>
+          <t>0,19; 1,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,49</t>
+          <t>0,45; 2,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,62</t>
+          <t>0,19; 1,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,14</t>
+          <t>0,25; 2,39</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,17</t>
+          <t>0,69; 2,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,02</t>
+          <t>1,0; 2,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,77</t>
+          <t>0,58; 1,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,6</t>
+          <t>0,52; 1,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,06</t>
+          <t>0,69; 2,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,62</t>
+          <t>1,16; 3,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,75</t>
+          <t>0,49; 1,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,78</t>
+          <t>0,87; 2,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,8</t>
+          <t>0,84; 1,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,55</t>
+          <t>1,31; 2,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,55</t>
+          <t>0,62; 1,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,85</t>
+          <t>0,81; 2,02</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,44 +1436,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2764</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1628</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2795</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2764</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1248</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1346</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>4392</t>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1321</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5420</t>
+          <t>809; 7097</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>759; 6696</t>
+          <t>0; 5018</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3664</t>
+          <t>0; 4144</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 5859</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5556</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>759; 6951</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3784</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>673; 7070</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3857</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4662</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5168</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1478; 9250</t>
+          <t>1798; 9105</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1371; 8175</t>
+          <t>1414; 8733</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>626; 5604</t>
+          <t>628; 5620</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4448</t>
+          <t>0; 4896</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5408</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8063</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5823</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8742</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4276</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7830</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5408</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8063</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4710</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13077</t>
+          <t>13282</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2801; 11140</t>
+          <t>2578; 10751</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4757; 14665</t>
+          <t>4366; 13677</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1759; 8492</t>
+          <t>2003; 8823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3582; 14406</t>
+          <t>2062; 10051</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2681; 10458</t>
+          <t>2781; 10522</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4112; 13807</t>
+          <t>4620; 14547</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2012; 9595</t>
+          <t>1786; 9458</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1999; 10416</t>
+          <t>4504; 15337</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6423; 17354</t>
+          <t>6832; 17823</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11003; 24016</t>
+          <t>10882; 24652</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4969; 14647</t>
+          <t>5149; 15381</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8022; 21161</t>
+          <t>8273; 21338</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1380</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1514</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1343</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1712</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2665</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4705</t>
+          <t>0; 2934</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4618</t>
+          <t>652; 5967</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4099</t>
+          <t>0; 3623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5668</t>
+          <t>0; 4791</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3844</t>
+          <t>0; 4895</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>654; 5744</t>
+          <t>0; 5351</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 4698</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4294</t>
+          <t>0; 5871</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>638; 5650</t>
+          <t>636; 5456</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1406; 7908</t>
+          <t>1420; 9151</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>624; 5279</t>
+          <t>627; 5357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>768; 7097</t>
+          <t>799; 7575</t>
         </is>
       </c>
     </row>
@@ -1997,37 +1997,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13052</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6372</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4925; 14519</t>
+          <t>4925; 15615</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8273; 19521</t>
+          <t>6869; 18014</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3221; 11189</t>
+          <t>3878; 11530</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4921; 17184</t>
+          <t>3633; 12623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5016; 14699</t>
+          <t>4603; 14566</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7140; 18015</t>
+          <t>7493; 19592</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3262; 11672</t>
+          <t>3113; 11453</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3723; 13517</t>
+          <t>5466; 18267</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11313; 24959</t>
+          <t>11689; 26042</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17317; 34048</t>
+          <t>17427; 33368</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8150; 20111</t>
+          <t>8009; 20213</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10516; 26295</t>
+          <t>10652; 26670</t>
         </is>
       </c>
     </row>
